--- a/Data/processed/nztargetyears_xl.xlsx
+++ b/Data/processed/nztargetyears_xl.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pelz\Documents\GitHub\2023_carbondebt\Data\processed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{7F2281BE-1A72-4CD1-A970-8FBDF7D93858}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F8AA2B-D3BA-48C4-BD26-2B9FA7C22A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nztargetyears" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nztargetyears!$A$1:$M$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">nztargetyears!$A$1:$M$164</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="272">
   <si>
     <t>r10</t>
   </si>
@@ -802,12 +802,6 @@
     <t>HTI</t>
   </si>
   <si>
-    <t>MEX</t>
-  </si>
-  <si>
-    <t>Assumed</t>
-  </si>
-  <si>
     <t>PAN</t>
   </si>
   <si>
@@ -973,7 +967,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1810,9 +1804,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M165"/>
+  <dimension ref="A1:M164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -3491,7 +3485,7 @@
         <v>2060</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M67" s="1" t="s">
         <v>22</v>
@@ -5774,26 +5768,26 @@
       <c r="C135" t="s">
         <v>227</v>
       </c>
-      <c r="E135" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135">
+      <c r="D135" t="s">
+        <v>15</v>
+      </c>
+      <c r="F135">
         <v>2050</v>
       </c>
       <c r="H135" t="s">
-        <v>42</v>
-      </c>
-      <c r="I135" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="K135" s="1">
         <v>2050</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="M135" s="1" t="s">
-        <v>228</v>
+        <v>18</v>
       </c>
     </row>
     <row r="136" spans="1:13" x14ac:dyDescent="0.25">
@@ -5860,7 +5854,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>211</v>
       </c>
@@ -5870,26 +5864,14 @@
       <c r="C138" t="s">
         <v>233</v>
       </c>
-      <c r="D138" t="s">
-        <v>15</v>
-      </c>
-      <c r="F138">
-        <v>2050</v>
-      </c>
       <c r="H138" t="s">
-        <v>18</v>
-      </c>
-      <c r="J138" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="K138" s="1">
-        <v>2050</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="J138"/>
+      <c r="K138"/>
+      <c r="L138"/>
+      <c r="M138" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
@@ -5897,10 +5879,10 @@
         <v>211</v>
       </c>
       <c r="B139" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C139" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H139" t="s">
         <v>42</v>
@@ -5917,10 +5899,10 @@
         <v>211</v>
       </c>
       <c r="B140" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C140" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H140" t="s">
         <v>42</v>
@@ -5937,10 +5919,10 @@
         <v>211</v>
       </c>
       <c r="B141" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C141" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H141" t="s">
         <v>42</v>
@@ -5957,10 +5939,10 @@
         <v>211</v>
       </c>
       <c r="B142" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C142" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H142" t="s">
         <v>42</v>
@@ -5977,10 +5959,10 @@
         <v>211</v>
       </c>
       <c r="B143" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C143" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H143" t="s">
         <v>42</v>
@@ -5997,10 +5979,10 @@
         <v>211</v>
       </c>
       <c r="B144" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C144" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H144" t="s">
         <v>42</v>
@@ -6017,10 +5999,10 @@
         <v>211</v>
       </c>
       <c r="B145" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C145" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H145" t="s">
         <v>42</v>
@@ -6037,10 +6019,10 @@
         <v>211</v>
       </c>
       <c r="B146" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C146" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H146" t="s">
         <v>42</v>
@@ -6057,10 +6039,10 @@
         <v>211</v>
       </c>
       <c r="B147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C147" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H147" t="s">
         <v>42</v>
@@ -6077,10 +6059,10 @@
         <v>211</v>
       </c>
       <c r="B148" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C148" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H148" t="s">
         <v>42</v>
@@ -6097,10 +6079,10 @@
         <v>211</v>
       </c>
       <c r="B149" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C149" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H149" t="s">
         <v>42</v>
@@ -6117,10 +6099,10 @@
         <v>211</v>
       </c>
       <c r="B150" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C150" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H150" t="s">
         <v>42</v>
@@ -6137,10 +6119,10 @@
         <v>211</v>
       </c>
       <c r="B151" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C151" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H151" t="s">
         <v>42</v>
@@ -6157,10 +6139,10 @@
         <v>211</v>
       </c>
       <c r="B152" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C152" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H152" t="s">
         <v>42</v>
@@ -6172,9 +6154,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="B153" t="s">
         <v>249</v>
@@ -6182,19 +6164,40 @@
       <c r="C153" t="s">
         <v>249</v>
       </c>
+      <c r="D153" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153" t="s">
+        <v>17</v>
+      </c>
+      <c r="F153">
+        <v>2050</v>
+      </c>
+      <c r="G153">
+        <v>2050</v>
+      </c>
       <c r="H153" t="s">
-        <v>42</v>
-      </c>
-      <c r="J153"/>
-      <c r="K153"/>
-      <c r="L153"/>
-      <c r="M153" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="I153" t="s">
+        <v>47</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K153" s="1">
+        <v>2050</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B154" t="s">
         <v>251</v>
@@ -6218,7 +6221,7 @@
         <v>46</v>
       </c>
       <c r="I154" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>252</v>
@@ -6235,13 +6238,13 @@
     </row>
     <row r="155" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B155" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C155" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D155" t="s">
         <v>15</v>
@@ -6259,10 +6262,10 @@
         <v>46</v>
       </c>
       <c r="I155" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K155" s="1">
         <v>2050</v>
@@ -6276,7 +6279,7 @@
     </row>
     <row r="156" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B156" t="s">
         <v>256</v>
@@ -6285,7 +6288,7 @@
         <v>256</v>
       </c>
       <c r="D156" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E156" t="s">
         <v>17</v>
@@ -6317,7 +6320,7 @@
     </row>
     <row r="157" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B157" t="s">
         <v>258</v>
@@ -6326,10 +6329,10 @@
         <v>258</v>
       </c>
       <c r="D157" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F157">
         <v>2050</v>
@@ -6358,48 +6361,48 @@
     </row>
     <row r="158" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B158" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C158" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D158" t="s">
         <v>15</v>
       </c>
       <c r="E158" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="F158">
-        <v>2050</v>
+        <v>2070</v>
       </c>
       <c r="G158">
-        <v>2050</v>
+        <v>2070</v>
       </c>
       <c r="H158" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="I158" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K158" s="1">
-        <v>2050</v>
+        <v>2070</v>
       </c>
       <c r="L158" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M158" s="1" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
     </row>
     <row r="159" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B159" t="s">
         <v>263</v>
@@ -6408,39 +6411,30 @@
         <v>263</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
-      </c>
-      <c r="E159" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F159">
-        <v>2070</v>
-      </c>
-      <c r="G159">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="H159" t="s">
-        <v>18</v>
-      </c>
-      <c r="I159" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>264</v>
       </c>
       <c r="K159" s="1">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M159" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B160" t="s">
         <v>265</v>
@@ -6449,30 +6443,30 @@
         <v>265</v>
       </c>
       <c r="D160" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F160">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="H160" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>266</v>
       </c>
       <c r="K160" s="1">
-        <v>2050</v>
+        <v>2030</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M160" s="1" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="161" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B161" t="s">
         <v>267</v>
@@ -6483,28 +6477,37 @@
       <c r="D161" t="s">
         <v>15</v>
       </c>
+      <c r="E161" t="s">
+        <v>56</v>
+      </c>
       <c r="F161">
-        <v>2030</v>
+        <v>2045</v>
+      </c>
+      <c r="G161">
+        <v>2045</v>
       </c>
       <c r="H161" t="s">
-        <v>46</v>
+        <v>18</v>
+      </c>
+      <c r="I161" t="s">
+        <v>19</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>268</v>
       </c>
       <c r="K161" s="1">
-        <v>2030</v>
+        <v>2045</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>17</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B162" t="s">
         <v>269</v>
@@ -6512,46 +6515,25 @@
       <c r="C162" t="s">
         <v>269</v>
       </c>
-      <c r="D162" t="s">
-        <v>15</v>
-      </c>
-      <c r="E162" t="s">
-        <v>56</v>
-      </c>
-      <c r="F162">
-        <v>2045</v>
-      </c>
-      <c r="G162">
-        <v>2045</v>
-      </c>
       <c r="H162" t="s">
-        <v>18</v>
-      </c>
-      <c r="I162" t="s">
-        <v>19</v>
-      </c>
-      <c r="J162" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K162" s="1">
-        <v>2045</v>
-      </c>
-      <c r="L162" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M162" s="1" t="s">
-        <v>18</v>
+        <v>42</v>
+      </c>
+      <c r="J162"/>
+      <c r="K162"/>
+      <c r="L162"/>
+      <c r="M162" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B163" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C163" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H163" t="s">
         <v>42</v>
@@ -6565,13 +6547,13 @@
     </row>
     <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B164" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C164" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H164" t="s">
         <v>42</v>
@@ -6583,28 +6565,8 @@
         <v>42</v>
       </c>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>262</v>
-      </c>
-      <c r="B165" t="s">
-        <v>273</v>
-      </c>
-      <c r="C165" t="s">
-        <v>273</v>
-      </c>
-      <c r="H165" t="s">
-        <v>42</v>
-      </c>
-      <c r="J165"/>
-      <c r="K165"/>
-      <c r="L165"/>
-      <c r="M165" t="s">
-        <v>42</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M165">
+  <autoFilter ref="A1:M164" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <filterColumn colId="12">
       <filters>
         <filter val="Assumed"/>
